--- a/assessment_forms/023_instrument_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/023_instrument_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -929,68 +929,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>experience_level_choices</t>
+          <t>ensemble_experience_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>experience_level_choices</t>
+          <t>ensemble_experience_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ensemble_experience_choices</t>
+          <t>music_reading_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sight_reading</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sight reading</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ensemble_experience_choices</t>
+          <t>music_reading_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>ear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Ear</t>
         </is>
       </c>
     </row>
@@ -1002,46 +1002,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sight_reading</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sight reading</t>
+          <t>Score</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>music_reading_choices</t>
+          <t>instrument_technique_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ear</t>
+          <t>bowing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ear</t>
+          <t>Bowing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>music_reading_choices</t>
+          <t>instrument_technique_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>finger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Finger</t>
         </is>
       </c>
     </row>
@@ -1053,46 +1053,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bowing</t>
+          <t>mouthpiece</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bowing</t>
+          <t>Mouthpiece</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>instrument_technique_choices</t>
+          <t>music_theory_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>finger</t>
+          <t>scales</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finger</t>
+          <t>Scales</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>instrument_technique_choices</t>
+          <t>music_theory_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mouthpiece</t>
+          <t>chord</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mouthpiece</t>
+          <t>Chord</t>
         </is>
       </c>
     </row>
@@ -1104,46 +1104,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>scales</t>
+          <t>harmony</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scales</t>
+          <t>Harmony</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>music_theory_choices</t>
+          <t>performance_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chord</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chord</t>
+          <t>Professional</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>music_theory_choices</t>
+          <t>performance_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>harmony</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1155,44 +1155,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>novice</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>performance_level_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>performance_level_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>novice</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>Novice</t>
         </is>
